--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:23</t>
+    <t xml:space="preserve">2026-09-24 01:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -852,13 +852,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15">
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.84</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -898,13 +898,13 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="17">
@@ -921,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="18">
@@ -1013,13 +1013,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="23">
@@ -1059,13 +1059,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="24">
@@ -1076,19 +1076,19 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="25">
@@ -1105,13 +1105,13 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="26">
@@ -1128,13 +1128,13 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:14</t>
+    <t xml:space="preserve">2026-10-01 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2021_aysen.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_aysen.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:09</t>
+    <t xml:space="preserve">2026-10-05 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
